--- a/Evaluation Folder/Input/DOE 11.7 12.7.xlsx
+++ b/Evaluation Folder/Input/DOE 11.7 12.7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0f9b98384af4391/Desktop/Morph/Python/Single/Tecan/Tecan_Reader/Evaluation Folder/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0f9b98384af4391/Desktop/Morph/Python/Foraging/Tecan/Tecan_Reader/Evaluation Folder/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_2239514312C9C1418E261313469F00B47C5BCCEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AC724A2-F31A-44CB-BBAE-13F727937CB3}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_223951431259CE716EE50713469F00B47C5BCCEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22FF76DB-875A-43AB-9C55-95C9AFCD7608}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="149">
   <si>
     <t>Method name: LS_241112_Fluorescence_Actino_Sample (Modified)</t>
   </si>
@@ -454,6 +454,9 @@
     <t>DOE 11.7</t>
   </si>
   <si>
+    <t>DOE 12.7</t>
+  </si>
+  <si>
     <t>f</t>
   </si>
   <si>
@@ -463,7 +466,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>DOE 12.7</t>
+    <t>Error</t>
   </si>
 </sst>
 </file>
@@ -8671,10 +8674,10 @@
         <v>143</v>
       </c>
       <c r="G245" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H245" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I245" t="s">
         <v>143</v>
@@ -8689,16 +8692,16 @@
         <v>143</v>
       </c>
       <c r="M245" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="N245" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O245" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P245" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q245" t="s">
         <v>143</v>
@@ -8713,16 +8716,16 @@
         <v>143</v>
       </c>
       <c r="U245" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="V245" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="W245" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="X245" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="246" spans="1:24" x14ac:dyDescent="0.45">
@@ -8739,64 +8742,64 @@
         <v>142</v>
       </c>
       <c r="E246" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F246" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G246" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H246" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P246" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="W246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="X246" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="247" spans="1:24" x14ac:dyDescent="0.45">
